--- a/BWI/bestwine_output/bestwine_Turkey.xlsx
+++ b/BWI/bestwine_output/bestwine_Turkey.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA44"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5352,6 +5352,91 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Meyland Exclusive Wine &amp; Spirit Store</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Meyland Exclusive Wine &amp; Spirit Store</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>31372</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Fethiye</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Muğla</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Fevzi Çakmak Cd. No:12</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>48300</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://meyland.com.tr</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>info@meyland.com.tr</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>+90 544 484 88 44</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/meylandbodrum</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>Özgürhan Özünal</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Turkey.xlsx
+++ b/BWI/bestwine_output/bestwine_Turkey.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AA48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5437,6 +5437,345 @@
       <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" s="2" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Turkey</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Turkey</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>13639</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Bağcılar</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Marmara Region</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Koçman Cad. 34212, Güneşli</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>34212</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-tr.com</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>nesli.uslu@metro-tr.com</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>+90 4445040</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>292116</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metroturkiye/</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Metrotoptancimarket</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/metroturkiye</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@MetroT%C3%BCrkiye</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>Benedykt Pacholczyk</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>Sales and Operations Director</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benedykt-pacholczyk-938122131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Turkey</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Turkey</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>13639</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Bağcılar</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Marmara Region</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Koçman Cad. 34212, Güneşli</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>34212</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-tr.com</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>nesli.uslu@metro-tr.com</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>+90 4445040</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>292116</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metroturkiye/</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Metrotoptancimarket</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/metroturkiye</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@MetroT%C3%BCrkiye</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>Nesli Uslu</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>Wine Category Executive</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nesli-uslu-247a44137/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Turkey</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Turkey</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>13639</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Bağcılar</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Marmara Region</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Koçman Cad. 34212, Güneşli</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>34212</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-tr.com</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>nesli.uslu@metro-tr.com</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>+90 4445040</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>292116</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metroturkiye/</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Metrotoptancimarket</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/metroturkiye</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@MetroT%C3%BCrkiye</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>Ekrem Altin</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Food Category Management</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ekrem-altin/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
